--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_Library\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE6D52B-A95F-41FF-A6DA-2C73E6E0BEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2114712C-177C-46E0-939E-A6E812C975A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12810" yWindow="525" windowWidth="21555" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9465" yWindow="1635" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,148 +20,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
-  <si>
-    <t>Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Corn</t>
-  </si>
-  <si>
-    <t>상자다. 딱히 의미가 있진 않다.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>옥수수다</t>
-  </si>
-  <si>
     <t>(name)</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Legend</t>
-  </si>
-  <si>
-    <t>의문의 모자</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>지역에 나타나는 금화</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>SellingPrice</t>
-  </si>
-  <si>
-    <t>Item_DummyBox_1</t>
-  </si>
-  <si>
-    <t>MaxStackCount</t>
-  </si>
-  <si>
-    <t>착용하면 공격력이 강해진다.</t>
-  </si>
-  <si>
     <t>캐릭터 전체 컨셉이나 스토리</t>
   </si>
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
   <si>
-    <t>Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Item_Corn_1</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>IconPath</t>
   </si>
   <si>
-    <t>상자</t>
-  </si>
-  <si>
-    <t>옥수수</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>화폐</t>
-  </si>
-  <si>
-    <t>Item_Potato_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Box_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>감자</t>
-  </si>
-  <si>
-    <t>감자다. 딱히 의미가 있진 않다.</t>
-  </si>
-  <si>
-    <t>Item_Carrot_1</t>
+    <t>Item_Healkit</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>당근</t>
+    <t>Item_Umbra</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>토끼가 좋아할 것 같다.</t>
+    <t>Item_Magnet</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ormal</t>
-    </r>
+    <t>회복키트</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Normal</t>
+    <t>움브라</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Icon/Icon_Item_Carrot_1</t>
+    <t>자석</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 100회복 시켜준다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>외계종족의 힘의 원천으로 이를 사용하면 강해질 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템들을 한 곳으로 끌어모은다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item/Magnet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item/Umbra</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item/HealKit</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +419,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -499,7 +428,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -721,266 +650,142 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
-    <col min="5" max="7" width="12.5703125" style="2"/>
-    <col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.5703125" style="2"/>
+    <col min="3" max="3" width="58.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.140625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="12.75">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="12.75">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="10" t="s">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2">
-        <v>100</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2">
-        <v>100</v>
-      </c>
-      <c r="G7" s="2">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2">
-        <v>20</v>
-      </c>
-      <c r="G8" s="2">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="2">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2">
-        <v>150</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
